--- a/erp-server/erp-server-plm/src/main/resources/excel/exportExcelProjectReportForms.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/exportExcelProjectReportForms.xlsx
@@ -202,7 +202,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,27 +219,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -708,165 +687,161 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1215,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BQ2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -1229,14 +1204,24 @@
     <col min="9" max="9" width="13.375" customWidth="1"/>
     <col min="10" max="10" width="11.75" customWidth="1"/>
     <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="14.75" customWidth="1"/>
+    <col min="15" max="15" width="14.375" customWidth="1"/>
     <col min="17" max="17" width="9.125" customWidth="1"/>
-    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="18" max="18" width="13.375" customWidth="1"/>
+    <col min="20" max="20" width="12.25" customWidth="1"/>
+    <col min="21" max="21" width="12.125" customWidth="1"/>
+    <col min="22" max="22" width="10.125" customWidth="1"/>
+    <col min="23" max="23" width="15.25" customWidth="1"/>
+    <col min="24" max="24" width="14.125" customWidth="1"/>
+    <col min="25" max="25" width="15.125" customWidth="1"/>
+    <col min="26" max="26" width="14.875" customWidth="1"/>
     <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="29" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:69">
+    <row r="1" s="1" customFormat="1" spans="1:29">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1324,103 +1309,63 @@
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
-      <c r="AJ1" s="3"/>
-      <c r="AK1" s="3"/>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="3"/>
-      <c r="AN1" s="3"/>
-      <c r="AO1" s="3"/>
-      <c r="AP1" s="3"/>
-      <c r="AQ1" s="3"/>
-      <c r="AR1" s="3"/>
-      <c r="AS1" s="3"/>
-      <c r="AT1" s="3"/>
-      <c r="AU1" s="3"/>
-      <c r="AV1" s="3"/>
-      <c r="AW1" s="3"/>
-      <c r="AX1" s="3"/>
-      <c r="AY1" s="3"/>
-      <c r="AZ1" s="3"/>
-      <c r="BA1" s="3"/>
-      <c r="BB1" s="3"/>
-      <c r="BC1" s="3"/>
-      <c r="BD1" s="3"/>
-      <c r="BE1" s="3"/>
-      <c r="BF1" s="3"/>
-      <c r="BG1" s="3"/>
-      <c r="BH1" s="3"/>
-      <c r="BI1" s="3"/>
-      <c r="BJ1" s="3"/>
-      <c r="BK1" s="3"/>
-      <c r="BL1" s="3"/>
-      <c r="BM1" s="3"/>
-      <c r="BN1" s="3"/>
-      <c r="BO1" s="3"/>
-      <c r="BP1" s="3"/>
-      <c r="BQ1" s="6"/>
     </row>
     <row r="2" s="2" customFormat="1" ht="12" spans="1:29">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="4" t="s">
         <v>47</v>
       </c>
       <c r="T2" s="2" t="s">

--- a/erp-server/erp-server-plm/src/main/resources/excel/exportExcelProjectReportForms.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/exportExcelProjectReportForms.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -1404,26 +1402,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
 </file>